--- a/DateBase/orders/Nhat 48_2026-3-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-19.xlsx
@@ -784,6 +784,9 @@
         <v xml:space="preserve">448_吊米 绿_hanging amaranthus
 green_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -842,7 +845,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105520554105355102051015571010554555100100355850402510680</v>
+        <v>0105520554105355102051015571010554555100100355850402510685</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -588,7 +588,7 @@
     </row>
     <row r="19">
       <c r="C19" t="str">
-        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+        <v>753_蝴蝶洋牡丹黄_butterfly  Ranunculus_undefined_1bunch</v>
       </c>
       <c r="F19" t="str">
         <v>5</v>
@@ -788,9 +788,227 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>10</v>
+      </c>
+      <c r="C43" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>251_暖暖_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>11</v>
+      </c>
+      <c r="C47" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>1</v>
+      </c>
+      <c r="C49" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>758_芍药凯瑟琳_Catherine_undefined_10stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>1</v>
+      </c>
+      <c r="C54" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>731_芍药冰点_undefined_undefined_10stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2</v>
+      </c>
+      <c r="C60" t="str">
+        <v>108_绣球深蓝_Hydrangea Dark Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F60" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>3</v>
+      </c>
+      <c r="C61" t="str">
+        <v>739_鸢尾花白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L66"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -845,7 +1063,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105520554105355102051015571010554555100100355850402510685</v>
+        <v>0105520554105355102051015571010554555100100355850402510685581086331203520704535207040510502055201010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-19.xlsx
@@ -1065,6 +1065,9 @@
       <c r="G2" t="str">
         <v>0105520554105355102051015571010554555100100355850402510685581086331203520704535207040510502055201010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nhat 48_2026-3-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-19.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,26 +443,23 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>377_一叶兰_undefined_undefined_1bunch</v>
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
       </c>
       <c r="F2" t="str">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
       <c r="C3" t="str">
-        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
       </c>
       <c r="F3" t="str">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="str">
-        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
       </c>
       <c r="F4" t="str">
         <v>5</v>
@@ -470,74 +467,77 @@
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>143_黑巴克_Black Baccara_Rosa rugosa Thunb._20stems</v>
+        <v>348_万年青_undefined_undefined_1bunch</v>
       </c>
       <c r="F5" t="str">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>263_乡村阳光_undefined_Rosa rugosa Thunb._20stems</v>
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
       </c>
       <c r="F6" t="str">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>2</v>
+      </c>
       <c r="C7" t="str">
-        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F7" t="str">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F8" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F9" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F10" t="str">
         <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>3</v>
-      </c>
-      <c r="C10" t="str">
-        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
-      </c>
-      <c r="F10" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="str">
-        <v>769_菟葵绿铃铛_undefined_undefined_undefinedundefined</v>
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>3</v>
       </c>
-    </row>
-    <row r="12">
       <c r="C12" t="str">
-        <v>594_绿毛球_undefined_undefined_1bunch</v>
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F12" t="str">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
-        <v>447_黄金球_craspedia_undefined_1bunch</v>
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F13" t="str">
         <v>5</v>
@@ -545,470 +545,77 @@
     </row>
     <row r="14">
       <c r="C14" t="str">
-        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
       </c>
       <c r="F14" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" t="str">
-        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+        <v>546_非洲菊绿宝石_undefined_undefined_1bunch</v>
       </c>
       <c r="F15" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="str">
+        <v>4</v>
+      </c>
       <c r="C16" t="str">
-        <v>406_千鸟飞燕 白_larkspur white_undefined_1bunch</v>
+        <v>791_菟葵黑_undefined_undefined_1bunch</v>
       </c>
       <c r="F16" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" t="str">
-        <v>873_洋牡丹九头蛇_undefined_undefined_1bunch</v>
+        <v>323_木绣球_Green snowball viburnum_undefined_1bunch</v>
       </c>
       <c r="F17" t="str">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>4</v>
-      </c>
       <c r="C18" t="str">
-        <v>739_鸢尾花白_undefined_undefined_1bunch</v>
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
       </c>
       <c r="F18" t="str">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="str">
-        <v>753_蝴蝶洋牡丹黄_butterfly  Ranunculus_undefined_1bunch</v>
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
       </c>
       <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>5</v>
       </c>
-    </row>
-    <row r="20">
       <c r="C20" t="str">
-        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
       </c>
       <c r="F20" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="str">
-        <v>398_小香球_undefined_undefined_1bunch</v>
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>558_油画小菊_Helenium_undefined_1bunch</v>
-      </c>
-      <c r="F22" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>5</v>
-      </c>
-      <c r="C23" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
-      </c>
-      <c r="F23" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="str">
-        <v>483_圣诞花_mimosa_undefined_1bunch</v>
-      </c>
-      <c r="F25" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
-red /green /orange / yellow_undefined_1bunch</v>
-      </c>
-      <c r="F26" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>843_灯台_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F27" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
-（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
-      </c>
-      <c r="F28" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>6</v>
-      </c>
-      <c r="C29" t="str">
-        <v>870_干花安娜绣球红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>7</v>
-      </c>
-      <c r="C30" t="str">
-        <v>633_干花安娜深红_undefined_undefined_1stem</v>
-      </c>
-      <c r="F30" t="str">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>8</v>
-      </c>
-      <c r="C31" t="str">
-        <v>737_木麻黄_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>9</v>
-      </c>
-      <c r="C32" t="str">
-        <v>324_小手球单瓣_Spiraea flower_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>320_雪柳花_Spiraea flower white_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="str">
-        <v>483_圣诞花_mimosa_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="str">
-        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
-      </c>
-      <c r="F35" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="str">
-        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
-      </c>
-      <c r="F36" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="str">
-        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
-      </c>
-      <c r="F37" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="str">
-        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
-      </c>
-      <c r="F38" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="str">
-        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
-      </c>
-      <c r="F39" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="str">
-        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
-      </c>
-      <c r="F40" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="C41" t="str" xml:space="preserve">
-        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
-green_undefined_1bunch</v>
-      </c>
-      <c r="F41" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="str">
-        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
-      </c>
-      <c r="F42" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>10</v>
-      </c>
-      <c r="C43" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F43" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="str">
-        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F44" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="str">
-        <v>251_暖暖_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F45" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="str">
-        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F46" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>11</v>
-      </c>
-      <c r="C47" t="str">
-        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
-      </c>
-      <c r="F47" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="str">
-        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
-      </c>
-      <c r="F48" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>1</v>
-      </c>
-      <c r="C49" t="str">
-        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
-      </c>
-      <c r="F49" t="str">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="str">
-        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
-      </c>
-      <c r="F50" t="str">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="str">
-        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
-      </c>
-      <c r="F51" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="str">
-        <v>758_芍药凯瑟琳_Catherine_undefined_10stems</v>
-      </c>
-      <c r="F52" t="str">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="str">
-        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
-      </c>
-      <c r="F53" t="str">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>1</v>
-      </c>
-      <c r="C54" t="str">
-        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
-      </c>
-      <c r="F54" t="str">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="str">
-        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
-      </c>
-      <c r="F55" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="str">
-        <v>731_芍药冰点_undefined_undefined_10stems</v>
-      </c>
-      <c r="F56" t="str">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="str">
-        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
-      </c>
-      <c r="F57" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="str">
-        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
-      </c>
-      <c r="F58" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="str">
-        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
-      </c>
-      <c r="F59" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
         <v>2</v>
-      </c>
-      <c r="C60" t="str">
-        <v>108_绣球深蓝_Hydrangea Dark Blue S_Hydrangea L._1stem</v>
-      </c>
-      <c r="F60" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>3</v>
-      </c>
-      <c r="C61" t="str">
-        <v>739_鸢尾花白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F61" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62" t="str">
-        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F62" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="C63" t="str">
-        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F63" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="C64" t="str">
-        <v>439_九星叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F64" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F65" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66" t="str">
-        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
-      </c>
-      <c r="F66" t="str">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1063,10 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105520554105355102051015571010554555100100355850402510685581086331203520704535207040510502055201010</v>
-      </c>
-      <c r="H2" t="str">
-        <v>CNY</v>
+        <v>080905512169111010205121010812662</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-19.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-19.xlsx
@@ -672,6 +672,9 @@
       <c r="G2" t="str">
         <v>080905512169111010205121010812662</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
